--- a/docs/reports/NCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
+++ b/docs/reports/NCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="KM Verification" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,13 +206,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,7 +228,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,7 +243,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,6 +296,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,7 +719,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -844,19 +861,19 @@
         <f>'Daily Breakdown'!J251</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="42">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="43">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="44">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="43">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -864,19 +881,19 @@
         <f>'Daily Breakdown'!K251</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="42">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="43">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="43">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="44">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -926,7 +943,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -998,7 +1021,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1038,7 +1061,7 @@
       <c r="C5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1078,7 +1101,7 @@
       <c r="C6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1118,7 +1141,7 @@
       <c r="C7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="45" t="n">
         <v>77.66</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1158,7 +1181,7 @@
       <c r="C8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="45" t="n">
         <v>77.75</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1198,7 +1221,7 @@
       <c r="C9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1238,7 +1261,7 @@
       <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1278,7 +1301,7 @@
       <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="45" t="n">
         <v>77.72</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1318,7 +1341,7 @@
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="45" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1358,7 +1381,7 @@
       <c r="C13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1398,7 +1421,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="45" t="n">
         <v>77.88</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1438,7 +1461,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1478,7 +1501,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1518,7 +1541,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="45" t="n">
         <v>77.66</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1558,7 +1581,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1598,7 +1621,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1638,7 +1661,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="45" t="n">
         <v>77.73</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1678,7 +1701,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="45" t="n">
         <v>77.61</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1718,7 +1741,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="45" t="n">
         <v>75.17</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1758,7 +1781,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1798,7 +1821,7 @@
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1838,7 +1861,7 @@
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1878,7 +1901,7 @@
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="45" t="n">
         <v>71.94</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1918,7 +1941,7 @@
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="45" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1958,7 +1981,7 @@
       <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -1998,7 +2021,7 @@
       <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="45" t="n">
         <v>77.7</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2038,7 +2061,7 @@
       <c r="C30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="45" t="n">
         <v>17.34</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2078,7 +2101,7 @@
       <c r="C31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="45" t="n">
         <v>77.67</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2118,7 +2141,7 @@
       <c r="C32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2158,7 +2181,7 @@
       <c r="C33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="45" t="n">
         <v>77.53</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2198,7 +2221,7 @@
       <c r="C34" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2238,7 +2261,7 @@
       <c r="C35" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="45" t="n">
         <v>76.94</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2278,7 +2301,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="45" t="n">
         <v>19.05</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2319,7 +2342,7 @@
         <f>SUM(C4:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="46">
         <f>SUM(D4:D36)</f>
         <v/>
       </c>
@@ -2328,7 +2351,7 @@
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>SUM(F4:F36)</f>
+        <f>SUMIF(E4:E36,"&gt;0",F4:F36)</f>
         <v/>
       </c>
       <c r="G37" s="24">
@@ -2366,7 +2389,7 @@
       <c r="C38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2406,7 +2429,7 @@
       <c r="C39" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2446,7 +2469,7 @@
       <c r="C40" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2486,7 +2509,7 @@
       <c r="C41" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2526,7 +2549,7 @@
       <c r="C42" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2566,7 +2589,7 @@
       <c r="C43" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2606,7 +2629,7 @@
       <c r="C44" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2646,7 +2669,7 @@
       <c r="C45" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2686,7 +2709,7 @@
       <c r="C46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2726,7 +2749,7 @@
       <c r="C47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="45" t="n">
         <v>24.76</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2766,7 +2789,7 @@
       <c r="C48" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="45" t="n">
         <v>17.34</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2806,7 +2829,7 @@
       <c r="C49" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2846,7 +2869,7 @@
       <c r="C50" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2886,7 +2909,7 @@
       <c r="C51" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2926,7 +2949,7 @@
       <c r="C52" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2966,7 +2989,7 @@
       <c r="C53" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3006,7 +3029,7 @@
       <c r="C54" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3046,7 +3069,7 @@
       <c r="C55" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3086,7 +3109,7 @@
       <c r="C56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3126,7 +3149,7 @@
       <c r="C57" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3166,7 +3189,7 @@
       <c r="C58" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="45" t="n">
         <v>77.34999999999999</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3206,7 +3229,7 @@
       <c r="C59" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E59" s="18" t="n">
@@ -3246,7 +3269,7 @@
       <c r="C60" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3286,7 +3309,7 @@
       <c r="C61" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3326,7 +3349,7 @@
       <c r="C62" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3366,7 +3389,7 @@
       <c r="C63" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3406,7 +3429,7 @@
       <c r="C64" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="45" t="n">
         <v>77.88</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3446,7 +3469,7 @@
       <c r="C65" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E65" s="18" t="n">
@@ -3486,7 +3509,7 @@
       <c r="C66" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="45" t="n">
         <v>77.72</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3526,7 +3549,7 @@
       <c r="C67" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3566,7 +3589,7 @@
       <c r="C68" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="45" t="n">
         <v>63.64</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3606,7 +3629,7 @@
       <c r="C69" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3646,7 +3669,7 @@
       <c r="C70" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="45" t="n">
         <v>77.72</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3686,7 +3709,7 @@
       <c r="C71" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="45" t="n">
         <v>2.68</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3726,7 +3749,7 @@
       <c r="C72" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3766,7 +3789,7 @@
       <c r="C73" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3806,7 +3829,7 @@
       <c r="C74" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3846,7 +3869,7 @@
       <c r="C75" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="45" t="n">
         <v>77.63</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3886,7 +3909,7 @@
       <c r="C76" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3926,7 +3949,7 @@
       <c r="C77" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="45" t="n">
         <v>30.02</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3966,7 +3989,7 @@
       <c r="C78" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4006,7 +4029,7 @@
       <c r="C79" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="45" t="n">
         <v>56.14</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4046,7 +4069,7 @@
       <c r="C80" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4087,7 +4110,7 @@
         <f>SUM(C38:C80)</f>
         <v/>
       </c>
-      <c r="D81" s="22">
+      <c r="D81" s="46">
         <f>SUM(D38:D80)</f>
         <v/>
       </c>
@@ -4096,7 +4119,7 @@
         <v/>
       </c>
       <c r="F81" s="23">
-        <f>SUM(F38:F80)</f>
+        <f>SUMIF(E38:E80,"&gt;0",F38:F80)</f>
         <v/>
       </c>
       <c r="G81" s="24">
@@ -4134,7 +4157,7 @@
       <c r="C82" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4174,7 +4197,7 @@
       <c r="C83" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4214,7 +4237,7 @@
       <c r="C84" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -4254,7 +4277,7 @@
       <c r="C85" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4294,7 +4317,7 @@
       <c r="C86" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E86" s="18" t="n">
@@ -4334,7 +4357,7 @@
       <c r="C87" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4374,7 +4397,7 @@
       <c r="C88" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4414,7 +4437,7 @@
       <c r="C89" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4454,7 +4477,7 @@
       <c r="C90" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4494,7 +4517,7 @@
       <c r="C91" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E91" s="18" t="n">
@@ -4534,7 +4557,7 @@
       <c r="C92" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4574,7 +4597,7 @@
       <c r="C93" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="45" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4614,7 +4637,7 @@
       <c r="C94" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E94" s="18" t="n">
@@ -4654,7 +4677,7 @@
       <c r="C95" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4694,7 +4717,7 @@
       <c r="C96" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4734,7 +4757,7 @@
       <c r="C97" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="45" t="n">
         <v>77.64</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4774,7 +4797,7 @@
       <c r="C98" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="45" t="n">
         <v>17.43</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4814,7 +4837,7 @@
       <c r="C99" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="45" t="n">
         <v>77.79000000000001</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4854,7 +4877,7 @@
       <c r="C100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="45" t="n">
         <v>20.19</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4894,7 +4917,7 @@
       <c r="C101" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="45" t="n">
         <v>77.51000000000001</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4934,7 +4957,7 @@
       <c r="C102" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="45" t="n">
         <v>77.64</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4974,7 +4997,7 @@
       <c r="C103" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5014,7 +5037,7 @@
       <c r="C104" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5054,7 +5077,7 @@
       <c r="C105" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5094,7 +5117,7 @@
       <c r="C106" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="45" t="n">
         <v>77.73</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5134,7 +5157,7 @@
       <c r="C107" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="45" t="n">
         <v>77.66</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5174,7 +5197,7 @@
       <c r="C108" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5214,7 +5237,7 @@
       <c r="C109" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5254,7 +5277,7 @@
       <c r="C110" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="45" t="n">
         <v>47.77</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5294,7 +5317,7 @@
       <c r="C111" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="45" t="n">
         <v>77.73</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5334,7 +5357,7 @@
       <c r="C112" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="45" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5374,7 +5397,7 @@
       <c r="C113" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="45" t="n">
         <v>76.77</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5414,7 +5437,7 @@
       <c r="C114" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E114" s="18" t="n">
@@ -5454,7 +5477,7 @@
       <c r="C115" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5494,7 +5517,7 @@
       <c r="C116" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5534,7 +5557,7 @@
       <c r="C117" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="45" t="n">
         <v>74.76000000000001</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5575,7 +5598,7 @@
         <f>SUM(C82:C117)</f>
         <v/>
       </c>
-      <c r="D118" s="22">
+      <c r="D118" s="46">
         <f>SUM(D82:D117)</f>
         <v/>
       </c>
@@ -5584,7 +5607,7 @@
         <v/>
       </c>
       <c r="F118" s="23">
-        <f>SUM(F82:F117)</f>
+        <f>SUMIF(E82:E117,"&gt;0",F82:F117)</f>
         <v/>
       </c>
       <c r="G118" s="24">
@@ -5622,7 +5645,7 @@
       <c r="C119" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5662,7 +5685,7 @@
       <c r="C120" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5702,7 +5725,7 @@
       <c r="C121" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5742,7 +5765,7 @@
       <c r="C122" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D122" s="17" t="n">
+      <c r="D122" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E122" s="18" t="n">
@@ -5782,7 +5805,7 @@
       <c r="C123" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D123" s="17" t="n">
+      <c r="D123" s="45" t="n">
         <v>77.88</v>
       </c>
       <c r="E123" s="18" t="n">
@@ -5822,7 +5845,7 @@
       <c r="C124" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5862,7 +5885,7 @@
       <c r="C125" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5902,7 +5925,7 @@
       <c r="C126" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="45" t="n">
         <v>77.67</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5942,7 +5965,7 @@
       <c r="C127" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -5982,7 +6005,7 @@
       <c r="C128" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="45" t="n">
         <v>77.73</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6022,7 +6045,7 @@
       <c r="C129" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6062,7 +6085,7 @@
       <c r="C130" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D130" s="17" t="n">
+      <c r="D130" s="45" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E130" s="18" t="n">
@@ -6102,7 +6125,7 @@
       <c r="C131" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="45" t="n">
         <v>77.73</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6142,7 +6165,7 @@
       <c r="C132" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6182,7 +6205,7 @@
       <c r="C133" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="45" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6222,7 +6245,7 @@
       <c r="C134" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="45" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6262,7 +6285,7 @@
       <c r="C135" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6302,7 +6325,7 @@
       <c r="C136" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="45" t="n">
         <v>77.64</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6342,7 +6365,7 @@
       <c r="C137" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6382,7 +6405,7 @@
       <c r="C138" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6422,7 +6445,7 @@
       <c r="C139" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6462,7 +6485,7 @@
       <c r="C140" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6502,7 +6525,7 @@
       <c r="C141" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6542,7 +6565,7 @@
       <c r="C142" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="45" t="n">
         <v>77.67</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6582,7 +6605,7 @@
       <c r="C143" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6622,7 +6645,7 @@
       <c r="C144" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6662,7 +6685,7 @@
       <c r="C145" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="45" t="n">
         <v>77.66</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6702,7 +6725,7 @@
       <c r="C146" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="45" t="n">
         <v>47.88</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6742,7 +6765,7 @@
       <c r="C147" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D147" s="17" t="n">
+      <c r="D147" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E147" s="18" t="n">
@@ -6782,7 +6805,7 @@
       <c r="C148" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6822,7 +6845,7 @@
       <c r="C149" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="45" t="n">
         <v>34.76</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6862,7 +6885,7 @@
       <c r="C150" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="45" t="n">
         <v>10.81</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6902,7 +6925,7 @@
       <c r="C151" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D151" s="17" t="n">
+      <c r="D151" s="45" t="n">
         <v>0.57</v>
       </c>
       <c r="E151" s="18" t="n">
@@ -6942,7 +6965,7 @@
       <c r="C152" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="45" t="n">
         <v>2.92</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -6983,7 +7006,7 @@
         <f>SUM(C119:C152)</f>
         <v/>
       </c>
-      <c r="D153" s="22">
+      <c r="D153" s="46">
         <f>SUM(D119:D152)</f>
         <v/>
       </c>
@@ -6992,7 +7015,7 @@
         <v/>
       </c>
       <c r="F153" s="23">
-        <f>SUM(F119:F152)</f>
+        <f>SUMIF(E119:E152,"&gt;0",F119:F152)</f>
         <v/>
       </c>
       <c r="G153" s="24">
@@ -7030,7 +7053,7 @@
       <c r="C154" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7070,7 +7093,7 @@
       <c r="C155" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7110,7 +7133,7 @@
       <c r="C156" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7150,7 +7173,7 @@
       <c r="C157" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7190,7 +7213,7 @@
       <c r="C158" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7230,7 +7253,7 @@
       <c r="C159" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7270,7 +7293,7 @@
       <c r="C160" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7310,7 +7333,7 @@
       <c r="C161" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7350,7 +7373,7 @@
       <c r="C162" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D162" s="17" t="n">
+      <c r="D162" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E162" s="18" t="n">
@@ -7390,7 +7413,7 @@
       <c r="C163" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7430,7 +7453,7 @@
       <c r="C164" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7470,7 +7493,7 @@
       <c r="C165" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D165" s="17" t="n">
+      <c r="D165" s="45" t="n">
         <v>77.72</v>
       </c>
       <c r="E165" s="18" t="n">
@@ -7510,7 +7533,7 @@
       <c r="C166" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7550,7 +7573,7 @@
       <c r="C167" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7590,7 +7613,7 @@
       <c r="C168" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D168" s="17" t="n">
+      <c r="D168" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E168" s="18" t="n">
@@ -7630,7 +7653,7 @@
       <c r="C169" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7670,7 +7693,7 @@
       <c r="C170" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="45" t="n">
         <v>77.7</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7710,7 +7733,7 @@
       <c r="C171" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7750,7 +7773,7 @@
       <c r="C172" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7790,7 +7813,7 @@
       <c r="C173" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7830,7 +7853,7 @@
       <c r="C174" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7870,7 +7893,7 @@
       <c r="C175" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7910,7 +7933,7 @@
       <c r="C176" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="45" t="n">
         <v>77.66</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7950,7 +7973,7 @@
       <c r="C177" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -7990,7 +8013,7 @@
       <c r="C178" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8030,7 +8053,7 @@
       <c r="C179" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D179" s="17" t="n">
+      <c r="D179" s="45" t="n">
         <v>77.62</v>
       </c>
       <c r="E179" s="18" t="n">
@@ -8070,7 +8093,7 @@
       <c r="C180" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8110,7 +8133,7 @@
       <c r="C181" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="45" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8150,7 +8173,7 @@
       <c r="C182" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D182" s="17" t="n">
+      <c r="D182" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E182" s="18" t="n">
@@ -8190,7 +8213,7 @@
       <c r="C183" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="45" t="n">
         <v>77.81</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8230,7 +8253,7 @@
       <c r="C184" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="45" t="n">
         <v>77.81</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8270,7 +8293,7 @@
       <c r="C185" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="45" t="n">
         <v>0</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8310,7 +8333,7 @@
       <c r="C186" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8350,7 +8373,7 @@
       <c r="C187" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8390,7 +8413,7 @@
       <c r="C188" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="45" t="n">
         <v>77.77</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8430,7 +8453,7 @@
       <c r="C189" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="45" t="n">
         <v>35.37</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8470,7 +8493,7 @@
       <c r="C190" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="45" t="n">
         <v>8.77</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8510,7 +8533,7 @@
       <c r="C191" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="45" t="n">
         <v>75.76000000000001</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8551,7 +8574,7 @@
         <f>SUM(C154:C191)</f>
         <v/>
       </c>
-      <c r="D192" s="22">
+      <c r="D192" s="46">
         <f>SUM(D154:D191)</f>
         <v/>
       </c>
@@ -8560,7 +8583,7 @@
         <v/>
       </c>
       <c r="F192" s="23">
-        <f>SUM(F154:F191)</f>
+        <f>SUMIF(E154:E191,"&gt;0",F154:F191)</f>
         <v/>
       </c>
       <c r="G192" s="24">
@@ -8598,7 +8621,7 @@
       <c r="C193" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="45" t="n">
         <v>76.89</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8638,7 +8661,7 @@
       <c r="C194" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D194" s="17" t="n">
+      <c r="D194" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E194" s="18" t="n">
@@ -8678,7 +8701,7 @@
       <c r="C195" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8718,7 +8741,7 @@
       <c r="C196" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="45" t="n">
         <v>77.81</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8758,7 +8781,7 @@
       <c r="C197" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8798,7 +8821,7 @@
       <c r="C198" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="45" t="n">
         <v>77.88</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8838,7 +8861,7 @@
       <c r="C199" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8878,7 +8901,7 @@
       <c r="C200" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D200" s="17" t="n">
+      <c r="D200" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E200" s="18" t="n">
@@ -8918,7 +8941,7 @@
       <c r="C201" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="45" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8958,7 +8981,7 @@
       <c r="C202" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="45" t="n">
         <v>77.81</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -8998,7 +9021,7 @@
       <c r="C203" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="45" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9038,7 +9061,7 @@
       <c r="C204" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9078,7 +9101,7 @@
       <c r="C205" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9118,7 +9141,7 @@
       <c r="C206" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9158,7 +9181,7 @@
       <c r="C207" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9198,7 +9221,7 @@
       <c r="C208" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9238,7 +9261,7 @@
       <c r="C209" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9278,7 +9301,7 @@
       <c r="C210" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9318,7 +9341,7 @@
       <c r="C211" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D211" s="17" t="n">
+      <c r="D211" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E211" s="18" t="n">
@@ -9358,7 +9381,7 @@
       <c r="C212" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D212" s="17" t="n">
+      <c r="D212" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E212" s="18" t="n">
@@ -9398,7 +9421,7 @@
       <c r="C213" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D213" s="17" t="n">
+      <c r="D213" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E213" s="18" t="n">
@@ -9438,7 +9461,7 @@
       <c r="C214" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D214" s="17" t="n">
+      <c r="D214" s="45" t="n">
         <v>74.37</v>
       </c>
       <c r="E214" s="18" t="n">
@@ -9478,7 +9501,7 @@
       <c r="C215" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D215" s="17" t="n">
+      <c r="D215" s="45" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E215" s="18" t="n">
@@ -9518,7 +9541,7 @@
       <c r="C216" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D216" s="17" t="n">
+      <c r="D216" s="45" t="n">
         <v>77.47</v>
       </c>
       <c r="E216" s="18" t="n">
@@ -9558,7 +9581,7 @@
       <c r="C217" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D217" s="17" t="n">
+      <c r="D217" s="45" t="n">
         <v>42.48</v>
       </c>
       <c r="E217" s="18" t="n">
@@ -9598,7 +9621,7 @@
       <c r="C218" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D218" s="17" t="n">
+      <c r="D218" s="45" t="n">
         <v>41.21</v>
       </c>
       <c r="E218" s="18" t="n">
@@ -9638,7 +9661,7 @@
       <c r="C219" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D219" s="17" t="n">
+      <c r="D219" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E219" s="18" t="n">
@@ -9678,7 +9701,7 @@
       <c r="C220" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D220" s="17" t="n">
+      <c r="D220" s="45" t="n">
         <v>8.44</v>
       </c>
       <c r="E220" s="18" t="n">
@@ -9718,7 +9741,7 @@
       <c r="C221" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D221" s="17" t="n">
+      <c r="D221" s="45" t="n">
         <v>2.49</v>
       </c>
       <c r="E221" s="18" t="n">
@@ -9759,7 +9782,7 @@
         <f>SUM(C193:C221)</f>
         <v/>
       </c>
-      <c r="D222" s="22">
+      <c r="D222" s="46">
         <f>SUM(D193:D221)</f>
         <v/>
       </c>
@@ -9768,7 +9791,7 @@
         <v/>
       </c>
       <c r="F222" s="23">
-        <f>SUM(F193:F221)</f>
+        <f>SUMIF(E193:E221,"&gt;0",F193:F221)</f>
         <v/>
       </c>
       <c r="G222" s="24">
@@ -9806,7 +9829,7 @@
       <c r="C223" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D223" s="17" t="n">
+      <c r="D223" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E223" s="18" t="n">
@@ -9846,7 +9869,7 @@
       <c r="C224" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D224" s="17" t="n">
+      <c r="D224" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E224" s="18" t="n">
@@ -9886,7 +9909,7 @@
       <c r="C225" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D225" s="17" t="n">
+      <c r="D225" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E225" s="18" t="n">
@@ -9926,7 +9949,7 @@
       <c r="C226" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D226" s="17" t="n">
+      <c r="D226" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E226" s="18" t="n">
@@ -9966,7 +9989,7 @@
       <c r="C227" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D227" s="17" t="n">
+      <c r="D227" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E227" s="18" t="n">
@@ -10006,7 +10029,7 @@
       <c r="C228" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D228" s="17" t="n">
+      <c r="D228" s="45" t="n">
         <v>77.87</v>
       </c>
       <c r="E228" s="18" t="n">
@@ -10046,7 +10069,7 @@
       <c r="C229" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D229" s="17" t="n">
+      <c r="D229" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E229" s="18" t="n">
@@ -10086,7 +10109,7 @@
       <c r="C230" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D230" s="17" t="n">
+      <c r="D230" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E230" s="18" t="n">
@@ -10126,7 +10149,7 @@
       <c r="C231" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D231" s="17" t="n">
+      <c r="D231" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E231" s="18" t="n">
@@ -10166,7 +10189,7 @@
       <c r="C232" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D232" s="17" t="n">
+      <c r="D232" s="45" t="n">
         <v>77.88</v>
       </c>
       <c r="E232" s="18" t="n">
@@ -10206,7 +10229,7 @@
       <c r="C233" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D233" s="17" t="n">
+      <c r="D233" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E233" s="18" t="n">
@@ -10246,7 +10269,7 @@
       <c r="C234" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D234" s="17" t="n">
+      <c r="D234" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E234" s="18" t="n">
@@ -10286,7 +10309,7 @@
       <c r="C235" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D235" s="17" t="n">
+      <c r="D235" s="45" t="n">
         <v>77.83</v>
       </c>
       <c r="E235" s="18" t="n">
@@ -10326,7 +10349,7 @@
       <c r="C236" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D236" s="17" t="n">
+      <c r="D236" s="45" t="n">
         <v>77.8</v>
       </c>
       <c r="E236" s="18" t="n">
@@ -10366,7 +10389,7 @@
       <c r="C237" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D237" s="17" t="n">
+      <c r="D237" s="45" t="n">
         <v>77.86</v>
       </c>
       <c r="E237" s="18" t="n">
@@ -10406,7 +10429,7 @@
       <c r="C238" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D238" s="17" t="n">
+      <c r="D238" s="45" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E238" s="18" t="n">
@@ -10446,7 +10469,7 @@
       <c r="C239" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D239" s="17" t="n">
+      <c r="D239" s="45" t="n">
         <v>77.7</v>
       </c>
       <c r="E239" s="18" t="n">
@@ -10486,7 +10509,7 @@
       <c r="C240" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D240" s="17" t="n">
+      <c r="D240" s="45" t="n">
         <v>77.84</v>
       </c>
       <c r="E240" s="18" t="n">
@@ -10526,7 +10549,7 @@
       <c r="C241" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D241" s="17" t="n">
+      <c r="D241" s="45" t="n">
         <v>77.69</v>
       </c>
       <c r="E241" s="18" t="n">
@@ -10566,7 +10589,7 @@
       <c r="C242" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D242" s="17" t="n">
+      <c r="D242" s="45" t="n">
         <v>77.72</v>
       </c>
       <c r="E242" s="18" t="n">
@@ -10606,7 +10629,7 @@
       <c r="C243" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D243" s="17" t="n">
+      <c r="D243" s="45" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E243" s="18" t="n">
@@ -10646,7 +10669,7 @@
       <c r="C244" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D244" s="17" t="n">
+      <c r="D244" s="45" t="n">
         <v>77.61</v>
       </c>
       <c r="E244" s="18" t="n">
@@ -10686,7 +10709,7 @@
       <c r="C245" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D245" s="17" t="n">
+      <c r="D245" s="45" t="n">
         <v>36.62</v>
       </c>
       <c r="E245" s="18" t="n">
@@ -10726,7 +10749,7 @@
       <c r="C246" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D246" s="17" t="n">
+      <c r="D246" s="45" t="n">
         <v>8.43</v>
       </c>
       <c r="E246" s="18" t="n">
@@ -10766,7 +10789,7 @@
       <c r="C247" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D247" s="17" t="n">
+      <c r="D247" s="45" t="n">
         <v>5.04</v>
       </c>
       <c r="E247" s="18" t="n">
@@ -10806,7 +10829,7 @@
       <c r="C248" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D248" s="17" t="n">
+      <c r="D248" s="45" t="n">
         <v>8.75</v>
       </c>
       <c r="E248" s="18" t="n">
@@ -10846,7 +10869,7 @@
       <c r="C249" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D249" s="17" t="n">
+      <c r="D249" s="45" t="n">
         <v>3.48</v>
       </c>
       <c r="E249" s="18" t="n">
@@ -10887,7 +10910,7 @@
         <f>SUM(C223:C249)</f>
         <v/>
       </c>
-      <c r="D250" s="22">
+      <c r="D250" s="46">
         <f>SUM(D223:D249)</f>
         <v/>
       </c>
@@ -10896,7 +10919,7 @@
         <v/>
       </c>
       <c r="F250" s="23">
-        <f>SUM(F223:F249)</f>
+        <f>SUMIF(E223:E249,"&gt;0",F223:F249)</f>
         <v/>
       </c>
       <c r="G250" s="24">
@@ -10931,7 +10954,7 @@
         <f>C37+C81+C118+C153+C192+C222+C250</f>
         <v/>
       </c>
-      <c r="D251" s="27">
+      <c r="D251" s="47">
         <f>D37+D81+D118+D153+D192+D222+D250</f>
         <v/>
       </c>
@@ -11006,7 +11029,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -11014,7 +11036,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -11512,7 +11533,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -24405,7 +24425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -24420,7 +24440,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="40" t="inlineStr">
         <is>
